--- a/Config/Datas/Tables/z_战斗规则_CombatRulesConfig.xlsx
+++ b/Config/Datas/Tables/z_战斗规则_CombatRulesConfig.xlsx
@@ -297,218 +297,248 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="24" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="24" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="24" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="24" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="42" customHeight="1">
-      <x:c r="A1" s="10" t="str">
-        <x:v>##</x:v>
-      </x:c>
-      <x:c r="B1" s="10" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="str">
-        <x:v>damageRandomMinBp</x:v>
-      </x:c>
-      <x:c r="D1" s="10" t="str">
-        <x:v>damageRandomMaxBp</x:v>
-      </x:c>
-      <x:c r="E1" s="10" t="str">
-        <x:v>criticalMultiplierBp</x:v>
-      </x:c>
-      <x:c r="F1" s="10" t="str">
-        <x:v>zeroHitDenominatorRateBp</x:v>
-      </x:c>
-      <x:c r="G1" s="10" t="str">
-        <x:v>zeroCritDenominatorRateBp</x:v>
-      </x:c>
-      <x:c r="H1" s="10" t="str">
-        <x:v>minAttackInterval</x:v>
-      </x:c>
-      <x:c r="I1" s="10" t="str">
-        <x:v>playerInvulnerabilitySeconds</x:v>
-      </x:c>
-      <x:c r="J1" s="10" t="str">
-        <x:v>simulationHz</x:v>
-      </x:c>
-      <x:c r="K1" s="10" t="str">
-        <x:v>maxCatchUpSteps</x:v>
-      </x:c>
-      <x:c r="L1" s="10" t="str">
-        <x:v>targetRefreshSeconds</x:v>
-      </x:c>
-      <x:c r="M1" s="10" t="str">
-        <x:v>spatialCellSize</x:v>
-      </x:c>
-      <x:c r="N1" s="10" t="str">
-        <x:v>worldUnitsPerPixel</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="25" customHeight="1">
-      <x:c r="A2" s="7" t="str">
-        <x:v>##type</x:v>
-      </x:c>
-      <x:c r="B2" s="7" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="C2" s="7" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="D2" s="7" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="E2" s="7" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="F2" s="7" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="G2" s="7" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="H2" s="7" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="I2" s="7" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="J2" s="7" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="K2" s="7" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="L2" s="7" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="M2" s="7" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="N2" s="7" t="str">
-        <x:v>float</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="25" customHeight="1">
-      <x:c r="A3" s="8" t="str">
-        <x:v>##var</x:v>
-      </x:c>
-      <x:c r="B3" s="8"/>
-      <x:c r="C3" s="8"/>
-      <x:c r="D3" s="8"/>
-      <x:c r="E3" s="8"/>
-      <x:c r="F3" s="8"/>
-      <x:c r="G3" s="8"/>
-      <x:c r="H3" s="8"/>
-      <x:c r="I3" s="8"/>
-      <x:c r="J3" s="8"/>
-      <x:c r="K3" s="8"/>
-      <x:c r="L3" s="8"/>
-      <x:c r="M3" s="8"/>
-      <x:c r="N3" s="8"/>
-    </x:row>
-    <x:row r="4" ht="65" customHeight="1">
-      <x:c r="A4" s="9" t="str">
-        <x:v>##</x:v>
-      </x:c>
-      <x:c r="B4" s="9" t="str">
-        <x:v>规则ID</x:v>
-      </x:c>
-      <x:c r="C4" s="9" t="str">
-        <x:v>伤害随机下限，万分比</x:v>
-      </x:c>
-      <x:c r="D4" s="9" t="str">
-        <x:v>伤害随机上限，万分比</x:v>
-      </x:c>
-      <x:c r="E4" s="9" t="str">
-        <x:v>暴击倍率，原文150%</x:v>
-      </x:c>
-      <x:c r="F4" s="9" t="str">
-        <x:v>命中分母为零时的概率，万分比</x:v>
-      </x:c>
-      <x:c r="G4" s="9" t="str">
-        <x:v>暴击分母为零时的概率，万分比</x:v>
-      </x:c>
-      <x:c r="H4" s="9" t="str">
-        <x:v>技能最短间隔，秒</x:v>
-      </x:c>
-      <x:c r="I4" s="9" t="str">
-        <x:v>玩家正数扣血后的无敌时间，秒</x:v>
-      </x:c>
-      <x:c r="J4" s="9" t="str">
-        <x:v>模拟频率，Hz</x:v>
-      </x:c>
-      <x:c r="K4" s="9" t="str">
-        <x:v>单渲染帧最多补算tick数</x:v>
-      </x:c>
-      <x:c r="L4" s="9" t="str">
-        <x:v>寻敌刷新周期，秒</x:v>
-      </x:c>
-      <x:c r="M4" s="9" t="str">
-        <x:v>空间网格边长，世界单位</x:v>
-      </x:c>
-      <x:c r="N4" s="9" t="str">
-        <x:v>资源像素转换为世界单位的比例</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="25" customHeight="1">
-      <x:c r="A5" s="4"/>
-      <x:c r="B5" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="4" t="n">
-        <x:v>8000</x:v>
-      </x:c>
-      <x:c r="D5" s="4" t="n">
-        <x:v>12000</x:v>
-      </x:c>
-      <x:c r="E5" s="4" t="n">
-        <x:v>15000</x:v>
-      </x:c>
-      <x:c r="F5" s="4" t="n">
-        <x:v>10000</x:v>
-      </x:c>
-      <x:c r="G5" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H5" s="4" t="n">
-        <x:v>0.05</x:v>
-      </x:c>
-      <x:c r="I5" s="4" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="J5" s="4" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="K5" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="L5" s="4" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="M5" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N5" s="4" t="n">
-        <x:v>0.01</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="24" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="24" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="24" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="24" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="24" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="24" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="24" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="10" t="str">
+        <v>##</v>
+      </c>
+      <c r="B1" s="10" t="str">
+        <v>id</v>
+      </c>
+      <c r="C1" s="10" t="str">
+        <v>damageRandomMinBp</v>
+      </c>
+      <c r="D1" s="10" t="str">
+        <v>damageRandomMaxBp</v>
+      </c>
+      <c r="E1" s="10" t="str">
+        <v>criticalMultiplierBp</v>
+      </c>
+      <c r="F1" s="10" t="str">
+        <v>zeroHitDenominatorRateBp</v>
+      </c>
+      <c r="G1" s="10" t="str">
+        <v>zeroCritDenominatorRateBp</v>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
+          <t>minAttackIntervalMilli</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
+          <t>playerInvulnerabilitySecondsMilli</t>
+        </is>
+      </c>
+      <c r="J1" s="10" t="str">
+        <v>simulationHz</v>
+      </c>
+      <c r="K1" s="10" t="str">
+        <v>maxCatchUpSteps</v>
+      </c>
+      <c r="L1" s="10" t="inlineStr">
+        <is>
+          <t>targetRefreshSecondsMilli</t>
+        </is>
+      </c>
+      <c r="M1" s="10" t="inlineStr">
+        <is>
+          <t>spatialCellSizeMilli</t>
+        </is>
+      </c>
+      <c r="N1" s="10" t="inlineStr">
+        <is>
+          <t>worldUnitsPerPixelMilli</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1">
+      <c r="A2" s="7" t="str">
+        <v>##type</v>
+      </c>
+      <c r="B2" s="7" t="str">
+        <v>int</v>
+      </c>
+      <c r="C2" s="7" t="str">
+        <v>int</v>
+      </c>
+      <c r="D2" s="7" t="str">
+        <v>int</v>
+      </c>
+      <c r="E2" s="7" t="str">
+        <v>int</v>
+      </c>
+      <c r="F2" s="7" t="str">
+        <v>int</v>
+      </c>
+      <c r="G2" s="7" t="str">
+        <v>int</v>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="str">
+        <v>int</v>
+      </c>
+      <c r="K2" s="7" t="str">
+        <v>int</v>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="8" t="str">
+        <v>##var</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+    </row>
+    <row r="4" ht="65" customHeight="1">
+      <c r="A4" s="9" t="str">
+        <v>##</v>
+      </c>
+      <c r="B4" s="9" t="str">
+        <v>规则ID</v>
+      </c>
+      <c r="C4" s="9" t="str">
+        <v>伤害随机下限，万分比</v>
+      </c>
+      <c r="D4" s="9" t="str">
+        <v>伤害随机上限，万分比</v>
+      </c>
+      <c r="E4" s="9" t="str">
+        <v>暴击倍率，原文150%</v>
+      </c>
+      <c r="F4" s="9" t="str">
+        <v>命中分母为零时的概率，万分比</v>
+      </c>
+      <c r="G4" s="9" t="str">
+        <v>暴击分母为零时的概率，万分比</v>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>技能最短间隔，秒；原单位×1000存整数，实际值=表值/1000，最多3位小数。</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>玩家正数扣血后的无敌时间，秒；原单位×1000存整数，实际值=表值/1000，最多3位小数。</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="str">
+        <v>模拟频率，Hz</v>
+      </c>
+      <c r="K4" s="9" t="str">
+        <v>单渲染帧最多补算tick数</v>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>寻敌刷新周期，秒；原单位×1000存整数，实际值=表值/1000，最多3位小数。</t>
+        </is>
+      </c>
+      <c r="M4" s="9" t="inlineStr">
+        <is>
+          <t>空间网格边长，世界单位；原单位×1000存整数，实际值=表值/1000，最多3位小数。</t>
+        </is>
+      </c>
+      <c r="N4" s="9" t="inlineStr">
+        <is>
+          <t>资源像素转换为世界单位的比例；原单位×1000存整数，实际值=表值/1000，最多3位小数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>50</v>
+      </c>
+      <c r="I5" s="4">
+        <v>500</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L5" s="4">
+        <v>100</v>
+      </c>
+      <c r="M5" s="4">
+        <v>1000</v>
+      </c>
+      <c r="N5" s="4">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Config/Datas/Tables/z_战斗规则_CombatRulesConfig.xlsx
+++ b/Config/Datas/Tables/z_战斗规则_CombatRulesConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbCombatRules" sheetId="1" r:id="Re92608c3c676454b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbCombatRules" sheetId="1" r:id="R7f87e57a81934d0f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -297,248 +297,236 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="10" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="24" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="24" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="24" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="24" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="24" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="24" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="24" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="24" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="24" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="42" customHeight="1">
-      <c r="A1" s="10" t="str">
-        <v>##</v>
-      </c>
-      <c r="B1" s="10" t="str">
-        <v>id</v>
-      </c>
-      <c r="C1" s="10" t="str">
-        <v>damageRandomMinBp</v>
-      </c>
-      <c r="D1" s="10" t="str">
-        <v>damageRandomMaxBp</v>
-      </c>
-      <c r="E1" s="10" t="str">
-        <v>criticalMultiplierBp</v>
-      </c>
-      <c r="F1" s="10" t="str">
-        <v>zeroHitDenominatorRateBp</v>
-      </c>
-      <c r="G1" s="10" t="str">
-        <v>zeroCritDenominatorRateBp</v>
-      </c>
-      <c r="H1" s="10" t="inlineStr">
-        <is>
-          <t>minAttackIntervalMilli</t>
-        </is>
-      </c>
-      <c r="I1" s="10" t="inlineStr">
-        <is>
-          <t>playerInvulnerabilitySecondsMilli</t>
-        </is>
-      </c>
-      <c r="J1" s="10" t="str">
-        <v>simulationHz</v>
-      </c>
-      <c r="K1" s="10" t="str">
-        <v>maxCatchUpSteps</v>
-      </c>
-      <c r="L1" s="10" t="inlineStr">
-        <is>
-          <t>targetRefreshSecondsMilli</t>
-        </is>
-      </c>
-      <c r="M1" s="10" t="inlineStr">
-        <is>
-          <t>spatialCellSizeMilli</t>
-        </is>
-      </c>
-      <c r="N1" s="10" t="inlineStr">
-        <is>
-          <t>worldUnitsPerPixelMilli</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="25" customHeight="1">
-      <c r="A2" s="7" t="str">
-        <v>##type</v>
-      </c>
-      <c r="B2" s="7" t="str">
-        <v>int</v>
-      </c>
-      <c r="C2" s="7" t="str">
-        <v>int</v>
-      </c>
-      <c r="D2" s="7" t="str">
-        <v>int</v>
-      </c>
-      <c r="E2" s="7" t="str">
-        <v>int</v>
-      </c>
-      <c r="F2" s="7" t="str">
-        <v>int</v>
-      </c>
-      <c r="G2" s="7" t="str">
-        <v>int</v>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="J2" s="7" t="str">
-        <v>int</v>
-      </c>
-      <c r="K2" s="7" t="str">
-        <v>int</v>
-      </c>
-      <c r="L2" s="7" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="M2" s="7" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N2" s="7" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="8" t="str">
-        <v>##var</v>
-      </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-    </row>
-    <row r="4" ht="65" customHeight="1">
-      <c r="A4" s="9" t="str">
-        <v>##</v>
-      </c>
-      <c r="B4" s="9" t="str">
-        <v>规则ID</v>
-      </c>
-      <c r="C4" s="9" t="str">
-        <v>伤害随机下限，万分比</v>
-      </c>
-      <c r="D4" s="9" t="str">
-        <v>伤害随机上限，万分比</v>
-      </c>
-      <c r="E4" s="9" t="str">
-        <v>暴击倍率，原文150%</v>
-      </c>
-      <c r="F4" s="9" t="str">
-        <v>命中分母为零时的概率，万分比</v>
-      </c>
-      <c r="G4" s="9" t="str">
-        <v>暴击分母为零时的概率，万分比</v>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>技能最短间隔，秒；原单位×1000存整数，实际值=表值/1000，最多3位小数。</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>玩家正数扣血后的无敌时间，秒；原单位×1000存整数，实际值=表值/1000，最多3位小数。</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="str">
-        <v>模拟频率，Hz</v>
-      </c>
-      <c r="K4" s="9" t="str">
-        <v>单渲染帧最多补算tick数</v>
-      </c>
-      <c r="L4" s="9" t="inlineStr">
-        <is>
-          <t>寻敌刷新周期，秒；原单位×1000存整数，实际值=表值/1000，最多3位小数。</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>空间网格边长，世界单位；原单位×1000存整数，实际值=表值/1000，最多3位小数。</t>
-        </is>
-      </c>
-      <c r="N4" s="9" t="inlineStr">
-        <is>
-          <t>资源像素转换为世界单位的比例；原单位×1000存整数，实际值=表值/1000，最多3位小数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>8000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4">
-        <v>50</v>
-      </c>
-      <c r="I5" s="4">
-        <v>500</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L5" s="4">
-        <v>100</v>
-      </c>
-      <c r="M5" s="4">
-        <v>1000</v>
-      </c>
-      <c r="N5" s="4">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="24" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="24" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="24" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="24" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="42" customHeight="1">
+      <x:c r="A1" s="10" t="str">
+        <x:v>##</x:v>
+      </x:c>
+      <x:c r="B1" s="10" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="C1" s="10" t="str">
+        <x:v>damageRandomMinBp</x:v>
+      </x:c>
+      <x:c r="D1" s="10" t="str">
+        <x:v>damageRandomMaxBp</x:v>
+      </x:c>
+      <x:c r="E1" s="10" t="str">
+        <x:v>criticalMultiplierBp</x:v>
+      </x:c>
+      <x:c r="F1" s="10" t="str">
+        <x:v>zeroHitDenominatorRateBp</x:v>
+      </x:c>
+      <x:c r="G1" s="10" t="str">
+        <x:v>zeroCritDenominatorRateBp</x:v>
+      </x:c>
+      <x:c r="H1" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">minAttackIntervalMilli</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I1" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">playerInvulnerabilitySecondsMilli</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J1" s="10" t="str">
+        <x:v>simulationHz</x:v>
+      </x:c>
+      <x:c r="K1" s="10" t="str">
+        <x:v>maxCatchUpSteps</x:v>
+      </x:c>
+      <x:c r="L1" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">targetRefreshSecondsMilli</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M1" s="10" t="str">
+        <x:v>spatialCellSizePixels</x:v>
+      </x:c>
+      <x:c r="N1" s="10" t="str">
+        <x:v>worldUnitsPerPixel</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="25" customHeight="1">
+      <x:c r="A2" s="7" t="str">
+        <x:v>##type</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="G2" s="7" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="H2" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I2" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J2" s="7" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="K2" s="7" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="L2" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M2" s="7" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="N2" s="7" t="str">
+        <x:v>float</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="25" customHeight="1">
+      <x:c r="A3" s="8" t="str">
+        <x:v>##var</x:v>
+      </x:c>
+      <x:c r="B3" s="8"/>
+      <x:c r="C3" s="8"/>
+      <x:c r="D3" s="8"/>
+      <x:c r="E3" s="8"/>
+      <x:c r="F3" s="8"/>
+      <x:c r="G3" s="8"/>
+      <x:c r="H3" s="8"/>
+      <x:c r="I3" s="8"/>
+      <x:c r="J3" s="8"/>
+      <x:c r="K3" s="8"/>
+      <x:c r="L3" s="8"/>
+      <x:c r="M3" s="8"/>
+      <x:c r="N3" s="8"/>
+    </x:row>
+    <x:row r="4" ht="65" customHeight="1">
+      <x:c r="A4" s="9" t="str">
+        <x:v>##</x:v>
+      </x:c>
+      <x:c r="B4" s="9" t="str">
+        <x:v>规则ID</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="str">
+        <x:v>伤害随机下限，万分比</x:v>
+      </x:c>
+      <x:c r="D4" s="9" t="str">
+        <x:v>伤害随机上限，万分比</x:v>
+      </x:c>
+      <x:c r="E4" s="9" t="str">
+        <x:v>暴击倍率，原文150%</x:v>
+      </x:c>
+      <x:c r="F4" s="9" t="str">
+        <x:v>命中分母为零时的概率，万分比</x:v>
+      </x:c>
+      <x:c r="G4" s="9" t="str">
+        <x:v>暴击分母为零时的概率，万分比</x:v>
+      </x:c>
+      <x:c r="H4" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">技能最短间隔，秒；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I4" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">玩家正数扣血后的无敌时间，秒；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J4" s="9" t="str">
+        <x:v>模拟频率，Hz</x:v>
+      </x:c>
+      <x:c r="K4" s="9" t="str">
+        <x:v>单渲染帧最多补算tick数</x:v>
+      </x:c>
+      <x:c r="L4" s="9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">寻敌刷新周期，秒；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M4" s="9" t="str">
+        <x:v>空间网格边长，逻辑像素；直接填写像素值，最多3位小数。</x:v>
+      </x:c>
+      <x:c r="N4" s="9" t="str">
+        <x:v>每逻辑像素对应的Unity世界单位；直接填写比例值。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="25" customHeight="1">
+      <x:c r="A5" s="4"/>
+      <x:c r="B5" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5" s="4" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+      <x:c r="D5" s="4" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="E5" s="4" t="n">
+        <x:v>15000</x:v>
+      </x:c>
+      <x:c r="F5" s="4" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="G5" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H5" s="4">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I5" s="4">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J5" s="4" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K5" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="L5" s="4">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="M5" s="4" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N5" s="4" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>